--- a/research/traditional_assets/database/data/bahrain/bahrain_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_investments_asset_management.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09080000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="E2">
-        <v>0.11</v>
+        <v>0.223</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,103 +600,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.5633456334563345</v>
+        <v>0.6899159663865547</v>
       </c>
       <c r="J2">
-        <v>0.5633456334563345</v>
+        <v>0.6899159663865547</v>
       </c>
       <c r="K2">
-        <v>4.23</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L2">
-        <v>0.5202952029520295</v>
+        <v>0.7100840336134453</v>
       </c>
       <c r="M2">
-        <v>2.22</v>
+        <v>2.233</v>
       </c>
       <c r="N2">
-        <v>0.06</v>
+        <v>0.03890243902439024</v>
       </c>
       <c r="O2">
-        <v>0.524822695035461</v>
+        <v>0.2642603550295858</v>
       </c>
       <c r="P2">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="Q2">
-        <v>0.06</v>
+        <v>0.03885017421602788</v>
       </c>
       <c r="R2">
-        <v>0.524822695035461</v>
+        <v>0.263905325443787</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.003000000000000114</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.001343484102104843</v>
       </c>
       <c r="U2">
-        <v>5.99</v>
+        <v>5.28</v>
       </c>
       <c r="V2">
-        <v>0.1618918918918919</v>
+        <v>0.09198606271777005</v>
       </c>
       <c r="W2">
-        <v>0.04674033149171272</v>
+        <v>0.09420289855072463</v>
       </c>
       <c r="X2">
-        <v>0.1880882822869645</v>
+        <v>0.1371939007382815</v>
       </c>
       <c r="Y2">
-        <v>-0.1413479507952518</v>
+        <v>-0.0429910021875569</v>
       </c>
       <c r="Z2">
-        <v>0.08522012578616353</v>
+        <v>0.1084677786892717</v>
       </c>
       <c r="AA2">
-        <v>0.0480083857442348</v>
+        <v>0.07483365235621184</v>
       </c>
       <c r="AB2">
-        <v>0.1625065738260271</v>
+        <v>0.1261323468294122</v>
       </c>
       <c r="AC2">
-        <v>-0.1144981880817923</v>
+        <v>-0.05129869447320035</v>
       </c>
       <c r="AD2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AG2">
-        <v>20.01</v>
+        <v>24.72</v>
       </c>
       <c r="AH2">
-        <v>0.4126984126984127</v>
+        <v>0.3432494279176201</v>
       </c>
       <c r="AI2">
-        <v>0.2247191011235955</v>
+        <v>0.2364066193853428</v>
       </c>
       <c r="AJ2">
-        <v>0.3509910542010173</v>
+        <v>0.3010228933268387</v>
       </c>
       <c r="AK2">
-        <v>0.1823899371069182</v>
+        <v>0.2032560434139122</v>
       </c>
       <c r="AL2">
-        <v>0.662</v>
+        <v>0.712</v>
       </c>
       <c r="AM2">
-        <v>0.662</v>
+        <v>0.712</v>
       </c>
       <c r="AO2">
-        <v>6.918429003021147</v>
+        <v>11.5308988764045</v>
       </c>
       <c r="AQ2">
-        <v>6.918429003021147</v>
+        <v>11.5308988764045</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09080000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="E3">
-        <v>0.11</v>
+        <v>0.223</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,103 +728,103 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.5633456334563345</v>
+        <v>0.6899159663865547</v>
       </c>
       <c r="J3">
-        <v>0.5633456334563345</v>
+        <v>0.6899159663865547</v>
       </c>
       <c r="K3">
-        <v>4.23</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L3">
-        <v>0.5202952029520295</v>
+        <v>0.7100840336134453</v>
       </c>
       <c r="M3">
-        <v>2.22</v>
+        <v>2.233</v>
       </c>
       <c r="N3">
-        <v>0.06</v>
+        <v>0.03890243902439024</v>
       </c>
       <c r="O3">
-        <v>0.524822695035461</v>
+        <v>0.2642603550295858</v>
       </c>
       <c r="P3">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="Q3">
-        <v>0.06</v>
+        <v>0.03885017421602788</v>
       </c>
       <c r="R3">
-        <v>0.524822695035461</v>
+        <v>0.263905325443787</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.003000000000000114</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.001343484102104843</v>
       </c>
       <c r="U3">
-        <v>5.99</v>
+        <v>5.28</v>
       </c>
       <c r="V3">
-        <v>0.1618918918918919</v>
+        <v>0.09198606271777005</v>
       </c>
       <c r="W3">
-        <v>0.04674033149171272</v>
+        <v>0.09420289855072463</v>
       </c>
       <c r="X3">
-        <v>0.1880882822869645</v>
+        <v>0.1371939007382815</v>
       </c>
       <c r="Y3">
-        <v>-0.1413479507952518</v>
+        <v>-0.0429910021875569</v>
       </c>
       <c r="Z3">
-        <v>0.08522012578616353</v>
+        <v>0.1084677786892717</v>
       </c>
       <c r="AA3">
-        <v>0.0480083857442348</v>
+        <v>0.07483365235621184</v>
       </c>
       <c r="AB3">
-        <v>0.1625065738260271</v>
+        <v>0.1261323468294122</v>
       </c>
       <c r="AC3">
-        <v>-0.1144981880817923</v>
+        <v>-0.05129869447320035</v>
       </c>
       <c r="AD3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AG3">
-        <v>20.01</v>
+        <v>24.72</v>
       </c>
       <c r="AH3">
-        <v>0.4126984126984127</v>
+        <v>0.3432494279176201</v>
       </c>
       <c r="AI3">
-        <v>0.2247191011235955</v>
+        <v>0.2364066193853428</v>
       </c>
       <c r="AJ3">
-        <v>0.3509910542010173</v>
+        <v>0.3010228933268387</v>
       </c>
       <c r="AK3">
-        <v>0.1823899371069182</v>
+        <v>0.2032560434139122</v>
       </c>
       <c r="AL3">
-        <v>0.662</v>
+        <v>0.712</v>
       </c>
       <c r="AM3">
-        <v>0.662</v>
+        <v>0.712</v>
       </c>
       <c r="AO3">
-        <v>6.918429003021147</v>
+        <v>11.5308988764045</v>
       </c>
       <c r="AQ3">
-        <v>6.918429003021147</v>
+        <v>11.5308988764045</v>
       </c>
     </row>
   </sheetData>
